--- a/results/job_matches_2026-09-27.xlsx
+++ b/results/job_matches_2026-09-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,42 +468,42 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Front End Engineer</t>
+          <t>Data Engineer 4 (Python, AWS, Spark, Kafka, SQL, Snowflake, Databricks, GenAI)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Prodapt Solutions</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.8</v>
+        <v>20.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Databricks, Google Cloud Platform, GCP, Kafka, Snowflake, Oracle, PostgreSQL</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, GCP, Hadoop, Hive</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00d8f8c4202abcea</t>
+          <t>https://www.indeed.com/viewjob?jk=d74f91161f0786df</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Apache Spark and Java)( Enterprise Platforms Technology)</t>
+          <t>Data Engineer 4 (Python, AWS, Spark, Kafka, SQL, Snowflake, Databricks, GenAI)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -513,50 +513,50 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>20.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Step Functions, S3, RDS, Azure, GCP</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, GCP, Hadoop, Hive</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c536a9bd99ef94e</t>
+          <t>https://www.indeed.com/viewjob?jk=94e06db5919f7704</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Apache Spark and Java)( Enterprise Platforms Technology)</t>
+          <t>AI Front End Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Prodapt Solutions</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>18.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Step Functions, S3, RDS, Azure, GCP</t>
+          <t>S3, RDS, Azure, Databricks, Google Cloud Platform, GCP, Kafka, Snowflake, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61acd17e8e4caf4c</t>
+          <t>https://www.indeed.com/viewjob?jk=00d8f8c4202abcea</t>
         </is>
       </c>
     </row>
@@ -608,165 +608,165 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer, Integrity</t>
+          <t>Senior Full Stack Engineer - AWS Cloud</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>National Basketball Association</t>
+          <t>Maximus</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Lanham, MD, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Snowflake, Data Modeling, ELT</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=836233526c2bfe4c</t>
+          <t>https://www.indeed.com/viewjob?jk=0f682845a41118d4</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Analytics Engineer, Integrity</t>
+          <t>Senior Full Stack Engineer - AWS Cloud</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>National Basketball Association</t>
+          <t>Maximus</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Lanham, MD, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Dimensional Modeling, ELT, dbt, MLOps</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=986e0cd967904817</t>
+          <t>https://www.indeed.com/viewjob?jk=d67a70dfbcdb3cc3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer, Data - FreeWheel</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Purple Wave Auction</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a2dcbf84370ecd2</t>
+          <t>https://www.indeed.com/viewjob?jk=7d55a501fc68d234</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - AWS Cloud</t>
+          <t>Engineer - Spatial Analytics</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Maximus</t>
+          <t>Community Transit</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lanham, MD, US USA</t>
+          <t>Everett, WA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB</t>
+          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f682845a41118d4</t>
+          <t>https://www.indeed.com/viewjob?jk=f5b39d8b03c9097b</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - AWS Cloud</t>
+          <t>Full-stack Engineer 5 (AI Platform &amp; Knowledge Library) (Enterprise Platforms Technology)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Maximus</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lanham, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d67a70dfbcdb3cc3</t>
+          <t>https://www.indeed.com/viewjob?jk=3c9d136b2b0b4aee</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Full Stack Engineer 4</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Purple Wave Auction</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d55a501fc68d234</t>
+          <t>https://www.indeed.com/viewjob?jk=2e1b607fdff26a44</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Engineer - Spatial Analytics</t>
+          <t>Software Engineer, Modernization</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Community Transit</t>
+          <t>Origami Risk LLC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Everett, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema, Power BI, CI/CD, Git</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,602 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5b39d8b03c9097b</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Full Stack Engineer 4</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2e1b607fdff26a44</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Full-stack Engineer 5 (Java, Spring Boot, AWS, CI/CD) (Enterprise Platforms Technology)</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b0e33ea940cfabaf</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Full-stack Engineer 4 (Cloud Native, Microservices &amp; AWS) ( Enterprise Platforms Technology)</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c52f54f8e5be210c</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Full Stack Engineer 4</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bca244a4074f26cb</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Full Stack Engineer - 4</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4acbff2d0e6ba792</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Full-stack Engineer 5 - Shopping (Remote-Eligible)</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a726f18ef6bec68d</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Full Stack Engineer - 4 (JavaScript, TypeScript)</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Richmond, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9360083577d366e1</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Full-stack Engineer 4</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=26af012597a937ac</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Full-Stack Engineer 4 (Python, Java, AWS, API, UI) (Enterprise Platforms Technology)</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0a471487d6e7ce5e</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Full Stack Engineer 4 (Bank Tech)</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Richmond, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=206971bfe0c7648e</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Full-stack Engineer 4</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f700dc035e701b44</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Full-stack Engineer 5</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cbde946ea5f19114</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Full-stack Engineer 4 (Remote-Eligible)</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3f21d9e3e95a919b</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Full-stack Engineer 4 (Cloud Native, Microservices &amp; AWS) ( Enterprise Platforms Technology)</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=befbf1e1c644225d</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer 4 (Python, AWS, SQL, GenAI) (Enterprise Platforms Technology)</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, CI/CD, Kubernetes, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1fc7880b49c1e317</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Software Engineer, Modernization</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Origami Risk LLC</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=c943bef31f88edac</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Full-stack Engineer 4 (Java, Spring Boot, AWS, CI/CD) (Enterprise Platforms Technology)</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bf46e42976391c6a</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-09-27.xlsx
+++ b/results/job_matches_2026-09-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,25 +573,25 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer 4</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Purple Wave Auction</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,67 +601,67 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b7a1bd8af02f9dc</t>
+          <t>https://www.indeed.com/viewjob?jk=7d55a501fc68d234</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - AWS Cloud</t>
+          <t>Engineer - Spatial Analytics</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Maximus</t>
+          <t>Community Transit</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Lanham, MD, US USA</t>
+          <t>Everett, WA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB</t>
+          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f682845a41118d4</t>
+          <t>https://www.indeed.com/viewjob?jk=f5b39d8b03c9097b</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - AWS Cloud</t>
+          <t>Full-stack Engineer 5 (AI Platform &amp; Knowledge Library) (Enterprise Platforms Technology)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Maximus</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Lanham, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,19 +671,19 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d67a70dfbcdb3cc3</t>
+          <t>https://www.indeed.com/viewjob?jk=3c9d136b2b0b4aee</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Software Engineer, Modernization</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Purple Wave Auction</t>
+          <t>Origami Risk LLC</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -692,159 +692,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7d55a501fc68d234</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Engineer - Spatial Analytics</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Community Transit</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Everett, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema, Power BI, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f5b39d8b03c9097b</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Full-stack Engineer 5 (AI Platform &amp; Knowledge Library) (Enterprise Platforms Technology)</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3c9d136b2b0b4aee</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Full Stack Engineer 4</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2e1b607fdff26a44</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Software Engineer, Modernization</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Origami Risk LLC</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=c943bef31f88edac</t>
         </is>

--- a/results/job_matches_2026-09-27.xlsx
+++ b/results/job_matches_2026-09-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,138 +573,103 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Engineer - Spatial Analytics</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Purple Wave Auction</t>
+          <t>Community Transit</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Everett, WA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt</t>
+          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d55a501fc68d234</t>
+          <t>https://www.indeed.com/viewjob?jk=f5b39d8b03c9097b</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Engineer - Spatial Analytics</t>
+          <t>Full-stack Engineer 5 (AI Platform &amp; Knowledge Library) (Enterprise Platforms Technology)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Community Transit</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Everett, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema, Power BI, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5b39d8b03c9097b</t>
+          <t>https://www.indeed.com/viewjob?jk=3c9d136b2b0b4aee</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5 (AI Platform &amp; Knowledge Library) (Enterprise Platforms Technology)</t>
+          <t>Software Engineer, Modernization</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Origami Risk LLC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3c9d136b2b0b4aee</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Software Engineer, Modernization</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Origami Risk LLC</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=c943bef31f88edac</t>
         </is>
